--- a/Web/TestCases/Categorias.xlsx
+++ b/Web/TestCases/Categorias.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nerea QA\PycharmProjects\KOVAI\Web\TestCases\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2BB7DF7-68A5-4A13-A705-E217399D60AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D82F9801-EA10-495D-B723-0D74A6723DD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -86,9 +86,6 @@
     <t>1. The categorie is created</t>
   </si>
   <si>
-    <t>PTE</t>
-  </si>
-  <si>
     <t>Create a categorie with all parameters.</t>
   </si>
   <si>
@@ -211,6 +208,9 @@
   <si>
     <t>No se avisa de que se va a borrar el rol
 Al borrar un rol, no se avisa/actualiza en la categoría</t>
+  </si>
+  <si>
+    <t>BL</t>
   </si>
 </sst>
 </file>
@@ -742,7 +742,7 @@
       </c>
       <c r="F3" s="1"/>
       <c r="G3" s="3" t="s">
-        <v>20</v>
+        <v>57</v>
       </c>
       <c r="H3" s="2"/>
     </row>
@@ -754,17 +754,17 @@
         <v>15</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F4" s="1"/>
       <c r="G4" s="3" t="s">
-        <v>20</v>
+        <v>57</v>
       </c>
       <c r="H4" s="2"/>
     </row>
@@ -776,22 +776,22 @@
         <v>16</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>12</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="6" spans="1:8" s="7" customFormat="1" ht="30" x14ac:dyDescent="0.25">
@@ -799,25 +799,25 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D6" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="E6" s="1" t="s">
+      <c r="F6" s="1" t="s">
         <v>29</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>30</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>12</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="7" spans="1:8" s="7" customFormat="1" ht="45" x14ac:dyDescent="0.25">
@@ -825,22 +825,22 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H7" s="1"/>
     </row>
@@ -849,22 +849,22 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E8" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="G8" s="3" t="s">
         <v>39</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>40</v>
       </c>
       <c r="H8" s="1"/>
     </row>
@@ -873,25 +873,25 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H9" s="8" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="10" spans="1:8" s="7" customFormat="1" ht="30" x14ac:dyDescent="0.25">
@@ -899,25 +899,25 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H10" s="8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="11" spans="1:8" s="7" customFormat="1" ht="30" x14ac:dyDescent="0.25">
@@ -925,23 +925,23 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D11" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E11" s="1" t="s">
         <v>48</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>49</v>
       </c>
       <c r="F11" s="1"/>
       <c r="G11" s="3" t="s">
         <v>12</v>
       </c>
       <c r="H11" s="8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
   </sheetData>
@@ -953,8 +953,6 @@
     <cfRule type="containsText" dxfId="2" priority="2" operator="containsText" text="BL">
       <formula>NOT(ISERROR(SEARCH("BL",G2)))</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G11">
     <cfRule type="containsText" dxfId="1" priority="3" operator="containsText" text="KO">
       <formula>NOT(ISERROR(SEARCH("KO",G2)))</formula>
     </cfRule>
